--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2421,10 +2421,10 @@
 </t>
   </si>
   <si>
-    <t>Exécutant de l’évènement documenté</t>
-  </si>
-  <si>
-    <t>Extension permettant d'ajouter un performer à l'élément event d'une Composition.</t>
+    <t>FR Performer Event Extension</t>
+  </si>
+  <si>
+    <t>Extension permettant d'ajouter l'exécutant de l'évènement documenté. Ajout d'un performer à l'élément event d'une Composition.</t>
   </si>
   <si>
     <t>Composition.event.modifierExtension</t>
